--- a/03_Outputs/Cartama/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Cartama/03_Ordenamiento/ordenamiento.xlsx
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E12" s="112">
-        <v>0.382793184431894</v>
+        <v>0.382793184431893</v>
       </c>
     </row>
   </sheetData>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.382793184431894</v>
+        <v>0.382793184431893</v>
       </c>
     </row>
   </sheetData>
